--- a/实际计算.xlsx
+++ b/实际计算.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18355" windowHeight="6840" activeTab="1"/>
+    <workbookView windowWidth="11060" windowHeight="6840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="当前模式0" sheetId="1" r:id="rId1"/>
@@ -2207,13 +2207,13 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>11.2</v>
+        <v>10.65</v>
       </c>
       <c r="C4">
-        <v>7.9</v>
+        <v>8.45</v>
       </c>
       <c r="D4">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -2411,13 +2411,13 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -2445,13 +2445,13 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18">
         <v>6</v>
@@ -2462,13 +2462,13 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -2496,13 +2496,13 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C21">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D21">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -2513,13 +2513,13 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C22">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D22">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -2547,13 +2547,13 @@
         <v>27</v>
       </c>
       <c r="B24">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -2564,13 +2564,13 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -2700,13 +2700,13 @@
         <v>36</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E33">
         <v>100</v>
@@ -2717,13 +2717,13 @@
         <v>37</v>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E34">
         <v>100</v>
@@ -2734,13 +2734,13 @@
         <v>38</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -2751,13 +2751,13 @@
         <v>39</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>3</v>
